--- a/out/Attention-Mamba1_repeat_1_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7769695850834731</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7769695850834731</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7769695850834731</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7769695850834731</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000104036541867652</v>
+        <v>-7.799307665787637e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1195180045462589</v>
+        <v>-0.0895990651288063</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.08967705820546427</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1197140089180402</v>
+        <v>-0.08984267945592024</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3306951148134856</v>
+        <v>0.5955362979557962</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5423116819178988</v>
+        <v>1.10237336795554</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0235619940853288</v>
+        <v>0.0424317996067125</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2582095696966639</v>
+        <v>0.5907454369590565</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04131970955680898</v>
+        <v>0.07441104741985818</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3172791315403897</v>
+        <v>0.6971214985182653</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05019825550601546</v>
+        <v>0.09040063474016564</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3763526255520442</v>
+        <v>0.8035046403281062</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01328388114714542</v>
+        <v>0.0239222729579882</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3526574180900385</v>
+        <v>0.7608331338291133</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007378310486558627</v>
+        <v>0.01329101425474998</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3541192581415919</v>
+        <v>0.7634691433707461</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01550615010576843</v>
+        <v>0.0279227810858223</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3777610098580788</v>
+        <v>0.8060433276554327</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006087911403926236</v>
+        <v>0.01096853810991366</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3744196257451512</v>
+        <v>0.8000299834605455</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004334936800096128</v>
+        <v>0.00780895616233524</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3769978376421423</v>
+        <v>0.804676511410564</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001703227128147758</v>
+        <v>0.003070623565385272</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3760659774156325</v>
+        <v>0.8030023534542273</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009645488820489561</v>
+        <v>0.001741421118221728</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.376290852654269</v>
+        <v>0.8034114212529159</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003637519384340607</v>
+        <v>0.0006596929845658545</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3760542077332996</v>
+        <v>0.80298916514123</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000167850789616339</v>
+        <v>0.0003065718054867767</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3760258215765813</v>
+        <v>0.8029420694614128</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.877869825396398e-05</v>
+        <v>0.0001096401917982644</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3759742813023829</v>
+        <v>0.8028534147913342</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.360244431470109e-05</v>
+        <v>2.886598836778916e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.375943124083657</v>
+        <v>0.8028013973491995</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.539715033180046e-06</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.375938109190816</v>
+        <v>0.8027963712867282</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>4.246422615251971e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3759338362732504</v>
+        <v>0.8027926800351098</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>1.274909021100856e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3759306686516856</v>
+        <v>0.8027909783162933</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>-2.504786695239595e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3759252993246978</v>
+        <v>0.8027853131593011</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3759193065912675</v>
+        <v>0.8027786584288671</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3759139388026891</v>
+        <v>0.8027731068978295</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0</v>
+        <v>-4.853353791035969e-06</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3759139755511808</v>
+        <v>0.8027681800470547</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3759140857966563</v>
+        <v>0.8027682902925303</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3759141592936399</v>
+        <v>0.802768363789514</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3759143430360991</v>
+        <v>0.8027685475319731</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3759158864727556</v>
+        <v>0.8027700909686296</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3759173564124287</v>
+        <v>0.8027715609083027</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1769695850834732</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3759186058611507</v>
+        <v>0.8027728103570246</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1769695850834732</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.375919965555348</v>
+        <v>0.802774170051222</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3759177606458387</v>
+        <v>0.8027719651417127</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3759173564124287</v>
+        <v>0.8027715609083027</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3759165111971167</v>
+        <v>0.8027707156929907</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.375917062424494</v>
+        <v>0.8027712669203679</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3759167316880676</v>
+        <v>0.8027709361839416</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3759164377001331</v>
+        <v>0.802770642196007</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-3.809276425334539</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3759165111971167</v>
+        <v>0.8027707156929907</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3759160702152147</v>
+        <v>0.8027702747110887</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3759159599697392</v>
+        <v>0.8027701644656132</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3759159232212475</v>
+        <v>0.8027701277171215</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-3.809276425334539</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3759160702152147</v>
+        <v>0.8027702747110887</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3759155924848211</v>
+        <v>0.8027697969806951</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3759165479456084</v>
+        <v>0.8027707524414824</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-3.809276425334539</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3759165111971167</v>
+        <v>0.8027707156929907</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3759161804606903</v>
+        <v>0.8027703849565643</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3759166214425922</v>
+        <v>0.8027708259384663</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3759159967182311</v>
+        <v>0.8027702012141051</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.375915812975772</v>
+        <v>0.802770017471646</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.375915408742362</v>
+        <v>0.8027696132382359</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3759145635270499</v>
+        <v>0.802768768022924</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3759145267785582</v>
+        <v>0.8027687312744323</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3759146737725255</v>
+        <v>0.8027688782683995</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3759146002755419</v>
+        <v>0.8027688047714159</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3759146737725255</v>
+        <v>0.8027688782683995</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3759147105210174</v>
+        <v>0.8027689150168914</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3759146002755419</v>
+        <v>0.8027688047714159</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3759150412574438</v>
+        <v>0.8027692457533179</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3759149310119683</v>
+        <v>0.8027691355078423</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3759148942634764</v>
+        <v>0.8027690987593503</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3759148207664927</v>
+        <v>0.8027690252623667</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.375914784018001</v>
+        <v>0.802768988513875</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3759145635270499</v>
+        <v>0.802768768022924</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3759144900300663</v>
+        <v>0.8027686945259404</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3759144165330827</v>
+        <v>0.8027686210289567</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3759144532815746</v>
+        <v>0.8027686577774487</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3759143430360991</v>
+        <v>0.8027685475319731</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3759144532815746</v>
+        <v>0.8027686577774487</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3759147472695091</v>
+        <v>0.8027689517653831</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000104036541867652</v>
+        <v>-0.0001065477369371802</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1195180045462589</v>
+        <v>-0.1224028853616547</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1196220410881266</v>
+        <v>-0.1225094330985919</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1197140089180402</v>
+        <v>-0.1226035362148735</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3306951148134856</v>
+        <v>0.3383733750478699</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5423116819178988</v>
+        <v>0.5547929031517669</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0235619940853288</v>
+        <v>0.02410903192866688</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2582095696966639</v>
+        <v>0.2640948039272898</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04131970955680898</v>
+        <v>0.04227902754668093</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3172791315403897</v>
+        <v>0.3245357813481905</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05019825550601546</v>
+        <v>0.05136371356915435</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3763526255520442</v>
+        <v>0.3849807822166353</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01328388114714542</v>
+        <v>0.01359212553837629</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3526574180900385</v>
+        <v>0.3607354478738597</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007378310486558627</v>
+        <v>0.007550006849674625</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3541192581415919</v>
+        <v>0.3622313611866522</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01550615010576843</v>
+        <v>0.01586518150541506</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3777610098580788</v>
+        <v>0.3864216930236085</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006087911403926236</v>
+        <v>0.006229607017971033</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383068</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3744196257451512</v>
+        <v>0.3830027262740179</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004334936800096128</v>
+        <v>0.004434983037936183</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.7612199440383068</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3769978376421423</v>
+        <v>0.3856410020497458</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001703227128147758</v>
+        <v>0.001742605972914281</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383068</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3760659774156325</v>
+        <v>0.384687407926101</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009645488820489561</v>
+        <v>0.0009876700795540981</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.376290852654269</v>
+        <v>0.3849177650861675</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003637519384340607</v>
+        <v>0.0003731468922795144</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3760542077332996</v>
+        <v>0.3846755952313633</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000167850789616339</v>
+        <v>0.0001722546313900037</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3760258215765813</v>
+        <v>0.3846466886185145</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.877869825396398e-05</v>
+        <v>5.958602354831795e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3759742813023829</v>
+        <v>0.3845942652389861</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.360244431470109e-05</v>
+        <v>1.407943006636009e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.375943124083657</v>
+        <v>0.3845624458027657</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.375938109190816</v>
+        <v>0.3845574309099249</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3759338362732504</v>
+        <v>0.3845531947408509</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3759306686516856</v>
+        <v>0.3845502108617453</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3759252993246978</v>
+        <v>0.384544767116739</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3759193065912675</v>
+        <v>0.3845387743833086</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3759139388026891</v>
+        <v>0.3845334065947302</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3759139755511808</v>
+        <v>0.3845334433432219</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3759140857966563</v>
+        <v>0.3845335535886975</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3759141592936399</v>
+        <v>0.3845336270856811</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3759143430360991</v>
+        <v>0.3845338108281403</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383067</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3759158864727556</v>
+        <v>0.3845353542647967</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-4.409276425334538</v>
+        <v>-0.7612199440383067</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3759173564124287</v>
+        <v>0.3845368242044698</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383066</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3759186058611507</v>
+        <v>0.3845380736531918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383068</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.375919965555348</v>
+        <v>0.3845394333473891</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-4.409276425334538</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3759177606458387</v>
+        <v>0.3845372284378798</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-4.409276425334538</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3759173564124287</v>
+        <v>0.3845368242044698</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-4.409276425334538</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3759165111971167</v>
+        <v>0.3845359789891578</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-4.409276425334538</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.375917062424494</v>
+        <v>0.3845365302165351</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-4.409276425334538</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3759167316880676</v>
+        <v>0.3845361994801087</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1769695850834732</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3759164377001331</v>
+        <v>0.3845359054921742</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-3.809276425334539</v>
+        <v>-0.5612199440383068</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3759165111971167</v>
+        <v>0.3845359789891578</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.5612199440383068</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3759160702152147</v>
+        <v>0.3845355380072559</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3759159599697392</v>
+        <v>0.3845354277617803</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.5612199440383067</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3759159232212475</v>
+        <v>0.3845353910132887</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-3.809276425334539</v>
+        <v>-0.5612199440383067</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3759160702152147</v>
+        <v>0.3845355380072559</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.5612199440383066</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3759155924848211</v>
+        <v>0.3845350602768622</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7769695850834731</v>
+        <v>-0.5612199440383068</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3759165479456084</v>
+        <v>0.3845360157376495</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-3.809276425334539</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3759165111971167</v>
+        <v>0.3845359789891578</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-4.409276425334538</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3759161804606903</v>
+        <v>0.3845356482527314</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-4.409276425334538</v>
+        <v>-2.857789548800827</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3759166214425922</v>
+        <v>0.3845360892346334</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-4.409276425334538</v>
+        <v>-1.809504746419567</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3759159967182311</v>
+        <v>0.3845354645102723</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1769695850834732</v>
+        <v>-0.7612199440383068</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.375915812975772</v>
+        <v>0.3845352807678131</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.375915408742362</v>
+        <v>0.384534876534403</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3759145635270499</v>
+        <v>0.3845340313190911</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3759145267785582</v>
+        <v>0.3845339945705994</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3759146737725255</v>
+        <v>0.3845341415645667</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3759146002755419</v>
+        <v>0.384534068067583</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3759146737725255</v>
+        <v>0.3845341415645667</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3759147105210174</v>
+        <v>0.3845341783130586</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7769695850834731</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3759146002755419</v>
+        <v>0.384534068067583</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.4870648583429531</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3759150412574438</v>
+        <v>0.384534509049485</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3759149310119683</v>
+        <v>0.3845343988040094</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3759148942634764</v>
+        <v>0.3845343620555175</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3759148207664927</v>
+        <v>0.3845342885585339</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.375914784018001</v>
+        <v>0.3845342518100422</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3759145635270499</v>
+        <v>0.3845340313190911</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3759144900300663</v>
+        <v>0.3845339578221075</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3759144165330827</v>
+        <v>0.3845338843251239</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3759144532815746</v>
+        <v>0.3845339210736158</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3759143430360991</v>
+        <v>0.3845338108281403</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3759144532815746</v>
+        <v>0.3845339210736158</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1769695850834732</v>
+        <v>0.287064858342953</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3759147472695091</v>
+        <v>0.3845342150615503</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.00735266599804163</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.287064858342953</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.008590386249125004</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.287064858342953</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01014910358935595</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.00999941024929285</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.005610008724033833</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.005855930037796497</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.006377250887453556</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.005865455605089664</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.006484991870820522</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.006457311101257801</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.287064858342953</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.007175135426223278</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.287064858342953</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.006512164138257504</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.287064858342953</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.006712679751217365</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.287064858342953</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.006323621608316898</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.287064858342953</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.007271816022694111</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006221923045814037</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.006294944323599339</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.006620011292397976</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.007030013017356396</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.007048622705042362</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.00688153225928545</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.007348318584263325</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.287064858342953</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.007160722278058529</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.287064858342953</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.007753797806799412</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.287064858342953</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.007191742770373821</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.287064858342953</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.007364247925579548</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.287064858342953</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.007289114408195019</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.287064858342953</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.007539897225797176</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.287064858342953</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.007605086080729961</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.287064858342953</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.008004623465240002</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.287064858342953</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01082652900367975</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.287064858342953</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.007192566059529781</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.287064858342953</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0075779864564538</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.287064858342953</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.007318031974136829</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.006874673999845982</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.007650078274309635</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.006521509028971195</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.006618398241698742</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.007828748784959316</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.007197641767561436</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.006735336966812611</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.007374909706413746</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.287064858342953</v>
+        <v>0.16</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.008765940554440022</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.287064858342953</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006675281561911106</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001065477369371802</v>
+        <v>-8.677021837199572e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1224028853616547</v>
+        <v>-0.0996823151528278</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.002494123764336109</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.005592647008597851</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.003483795560896397</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.004789755679666996</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.004320177249610424</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.004670177586376667</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.004549018107354641</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.005470304749906063</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.004442875273525715</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.00462589506059885</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.004136904142796993</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.004065119661390781</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.004421568475663662</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1225094330985919</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0058962507173419</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1226035362148735</v>
+        <v>-0.09985320430113002</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3383733750478699</v>
+        <v>0.3024725147330852</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.002410854212939739</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5547929031517669</v>
+        <v>0.505672583469492</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02410903192866688</v>
+        <v>0.02155106658257108</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.003851224668323994</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2640948039272898</v>
+        <v>0.2458170761228423</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04227902754668093</v>
+        <v>0.03779322788242955</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.004623142071068287</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3245357813481905</v>
+        <v>0.2998454569562301</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05136371356915435</v>
+        <v>0.04591430853235892</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.002010752446949482</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3849807822166353</v>
+        <v>0.3538776175777568</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01359212553837629</v>
+        <v>0.01215024144277921</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.002061718143522739</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3607354478738597</v>
+        <v>0.3322045471466817</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007550006849674625</v>
+        <v>0.006748390282562545</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.007035522721707821</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3622313611866522</v>
+        <v>0.3335412075294275</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01586518150541506</v>
+        <v>0.01418216678915515</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.004081328399479389</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3864216930236085</v>
+        <v>0.3551645029308307</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006229607017971033</v>
+        <v>0.005568360819095316</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.001831871457397938</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7612199440383068</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3830027262740179</v>
+        <v>0.3521079192220929</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004434983037936183</v>
+        <v>0.003964075746033861</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0002589216455817223</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7612199440383068</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3856410020497458</v>
+        <v>0.3544653876541187</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001742605972914281</v>
+        <v>0.001556574878672434</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.001307317055761814</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7612199440383068</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.384687407926101</v>
+        <v>0.3536127314088778</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009876700795540981</v>
+        <v>0.0008813125710304448</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.0002074176445603371</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3849177650861675</v>
+        <v>0.3538180554728247</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003731468922795144</v>
+        <v>0.0003332183384363358</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.0008776066824793816</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3846755952313633</v>
+        <v>0.3536009283977204</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001722546313900037</v>
+        <v>0.0001535383038519288</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.0008086906746029854</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3846466886185145</v>
+        <v>0.3535745460856072</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.958602354831795e-05</v>
+        <v>5.312742119348616e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.001607649959623814</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3845942652389861</v>
+        <v>0.3535271296331729</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.407943006636009e-05</v>
+        <v>1.217148705972408e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.002213354222476482</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3845624458027657</v>
+        <v>0.3534982898033582</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.539715033180046e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.002100919373333454</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3845574309099249</v>
+        <v>0.3534932763998017</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.002211947925388813</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3845531947408509</v>
+        <v>0.3534889307739923</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.001019853167235851</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3845502108617453</v>
+        <v>0.3534855804191995</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.001627353020012379</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.384544767116739</v>
+        <v>0.3534802110922118</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.00235563050955534</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3845387743833086</v>
+        <v>0.3534742183587814</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.002762009389698505</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.287064858342953</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3845334065947302</v>
+        <v>0.3534688505702031</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.002996171824634075</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.287064858342953</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3845334433432219</v>
+        <v>0.3534688873186947</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.002552864141762257</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.287064858342953</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3845335535886975</v>
+        <v>0.3534689975641703</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.002065935172140598</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.287064858342953</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3845336270856811</v>
+        <v>0.3534690710611539</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.002934104762971401</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.287064858342953</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3845338108281403</v>
+        <v>0.3534692548036131</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.003941447474062443</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7612199440383067</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3845353542647967</v>
+        <v>0.3534707982402696</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002963925711810589</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7612199440383067</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3845368242044698</v>
+        <v>0.3534722681799426</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0009508403018116951</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7612199440383066</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3845380736531918</v>
+        <v>0.3534735176286646</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.07801438868045807</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7612199440383068</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3845394333473891</v>
+        <v>0.3534748773228619</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01539632584899664</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3845372284378798</v>
+        <v>0.3534726724133526</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001553810201585293</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3845368242044698</v>
+        <v>0.3534722681799426</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.007292834110558033</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3845359789891578</v>
+        <v>0.3534714229646306</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.001632294617593288</v>
       </c>
       <c r="JB92" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3845365302165351</v>
+        <v>0.3534719741920079</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.001219081692397594</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3845361994801087</v>
+        <v>0.3534716434555815</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0002464940771460533</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3845359054921742</v>
+        <v>0.353471349467647</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0006235865876078606</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5612199440383068</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3845359789891578</v>
+        <v>0.3534714229646306</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>4.375819116830826e-05</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5612199440383068</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3845355380072559</v>
+        <v>0.3534709819827287</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>5.811359733343124e-05</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3845354277617803</v>
+        <v>0.3534708717372532</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0001672981306910515</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5612199440383067</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3845353910132887</v>
+        <v>0.3534708349887615</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-6.233993917703629e-05</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5612199440383067</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3845355380072559</v>
+        <v>0.3534709819827287</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.006320119835436344</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5612199440383066</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3845350602768622</v>
+        <v>0.3534705042523351</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.006587130017578602</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5612199440383068</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3845360157376495</v>
+        <v>0.3534714597131223</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003054832108318806</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.809504746419567</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3845359789891578</v>
+        <v>0.3534714229646306</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.0005223127081990242</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3845356482527314</v>
+        <v>0.3534710922282042</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.001063398085534573</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.857789548800827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3845360892346334</v>
+        <v>0.3534715332101062</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.0002495450899004936</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.809504746419567</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3845354645102723</v>
+        <v>0.3534709084857451</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0004492616280913353</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7612199440383068</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3845352807678131</v>
+        <v>0.3534707247432859</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.0006792200729250908</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.384534876534403</v>
+        <v>0.3534703205098759</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.001431002281606197</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3845340313190911</v>
+        <v>0.3534694752945639</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.001804214902222157</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3845339945705994</v>
+        <v>0.3534694385460722</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001552673988044262</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3845341415645667</v>
+        <v>0.3534695855400395</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.001286194659769535</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.384534068067583</v>
+        <v>0.3534695120430558</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.004203951917588711</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3845341415645667</v>
+        <v>0.3534695855400395</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0005159592255949974</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3845341783130586</v>
+        <v>0.3534696222885314</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.002637431956827641</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4870648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.384534068067583</v>
+        <v>0.3534695120430558</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>4.78820875287056e-05</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4870648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.384534509049485</v>
+        <v>0.3534699530249578</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0008846716955304146</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3845343988040094</v>
+        <v>0.3534698427794822</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0003505991771817207</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3845343620555175</v>
+        <v>0.3534698060309903</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.0008834348991513252</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3845342885585339</v>
+        <v>0.3534697325340067</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.0007661161944270134</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.287064858342953</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3845342518100422</v>
+        <v>0.353469695785515</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.0009679654613137245</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.287064858342953</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3845340313190911</v>
+        <v>0.3534694752945639</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.001674908213317394</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.287064858342953</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3845339578221075</v>
+        <v>0.3534694017975803</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.00139192771166563</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.287064858342953</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3845338843251239</v>
+        <v>0.3534693283005967</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.001267603598535061</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.287064858342953</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3845339210736158</v>
+        <v>0.3534693650490886</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.002019877545535564</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.287064858342953</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3845338108281403</v>
+        <v>0.3534692548036131</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.002995423041284084</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.287064858342953</v>
+        <v>0.9299999999999997</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3845339210736158</v>
+        <v>0.3534693650490886</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.002213896252214909</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.287064858342953</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3845342150615503</v>
+        <v>0.3534696590370231</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.00735266599804163</v>
+        <v>0.007352686487138271</v>
       </c>
       <c r="JB2" t="n">
         <v>0.1199999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.008590386249125004</v>
+        <v>0.008590373210608959</v>
       </c>
       <c r="JB3" t="n">
         <v>0.1199999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.01014910358935595</v>
+        <v>0.01014911103993654</v>
       </c>
       <c r="JB4" t="n">
         <v>0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.00999941024929285</v>
+        <v>0.009999413974583149</v>
       </c>
       <c r="JB5" t="n">
         <v>0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.005610008724033833</v>
+        <v>0.005609984509646893</v>
       </c>
       <c r="JB6" t="n">
         <v>0.5799999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.005855930037796497</v>
+        <v>0.005855935625731945</v>
       </c>
       <c r="JB7" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.006377250887453556</v>
+        <v>0.006377263925969601</v>
       </c>
       <c r="JB8" t="n">
         <v>0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.005865455605089664</v>
+        <v>0.005865463055670261</v>
       </c>
       <c r="JB9" t="n">
         <v>0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.006484991870820522</v>
+        <v>0.006484984420239925</v>
       </c>
       <c r="JB10" t="n">
         <v>0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.006457311101257801</v>
+        <v>0.006457324139773846</v>
       </c>
       <c r="JB11" t="n">
         <v>0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.007175135426223278</v>
+        <v>0.007175183854997158</v>
       </c>
       <c r="JB12" t="n">
         <v>0.8599999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.006512164138257504</v>
+        <v>0.006512167863547802</v>
       </c>
       <c r="JB13" t="n">
         <v>0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.006712679751217365</v>
+        <v>0.006712666712701321</v>
       </c>
       <c r="JB14" t="n">
         <v>0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.006323621608316898</v>
+        <v>0.006323584355413914</v>
       </c>
       <c r="JB15" t="n">
         <v>0.4399999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.007271816022694111</v>
+        <v>0.007271823473274708</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.006221923045814037</v>
+        <v>0.006221937946975231</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.006294944323599339</v>
+        <v>0.006294966675341129</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.006620011292397976</v>
+        <v>0.006620028056204319</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.5799999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.007030013017356396</v>
+        <v>0.007029996253550053</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.007048622705042362</v>
+        <v>0.00704862829297781</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.00688153225928545</v>
+        <v>0.006881535984575748</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.007348318584263325</v>
+        <v>0.007348365150392056</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.007160722278058529</v>
+        <v>0.007160716690123081</v>
       </c>
       <c r="JB24" t="n">
         <v>0.4399999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.007753797806799412</v>
+        <v>0.007753769867122173</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.007191742770373821</v>
+        <v>0.007191765122115612</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.007364247925579548</v>
+        <v>0.007364260964095592</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.007289114408195019</v>
+        <v>0.007289131172001362</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.007539897225797176</v>
+        <v>0.007539915852248669</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.007605086080729961</v>
+        <v>0.007605091668665409</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.008004623465240002</v>
+        <v>0.008004629053175449</v>
       </c>
       <c r="JB31" t="n">
         <v>0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.01082652900367975</v>
+        <v>0.0108265234157443</v>
       </c>
       <c r="JB32" t="n">
         <v>0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.007192566059529781</v>
+        <v>0.007192564196884632</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.0075779864564538</v>
+        <v>0.007577992044389248</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.007318031974136829</v>
+        <v>0.00731803011149168</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.006874673999845982</v>
+        <v>0.006874662823975086</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.007650078274309635</v>
+        <v>0.007650054059922695</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.006521509028971195</v>
+        <v>0.006521531380712986</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.006618398241698742</v>
+        <v>0.006618390791118145</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.007828748784959316</v>
+        <v>0.007828752510249615</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.007197641767561436</v>
+        <v>0.007197652943432331</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.007374909706413746</v>
+        <v>0.007374905981123447</v>
       </c>
       <c r="JB43" t="n">
         <v>0.16</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.008765940554440022</v>
+        <v>0.008765962906181812</v>
       </c>
       <c r="JB44" t="n">
         <v>0.02000000000000007</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.006675281561911106</v>
+        <v>0.006675294600427151</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.5799999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.002494123764336109</v>
+        <v>0.002494142390787601</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.005592647008597851</v>
+        <v>0.005592669360339642</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.003483795560896397</v>
+        <v>0.00348376389592886</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.004789755679666996</v>
+        <v>0.004789761267602444</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.004320177249610424</v>
+        <v>0.004320179112255573</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.004670177586376667</v>
+        <v>0.004670205526053905</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.004549018107354641</v>
+        <v>0.004548982717096806</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.005470304749906063</v>
+        <v>0.00547028798609972</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.004442875273525715</v>
+        <v>0.004442864097654819</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.00462589506059885</v>
+        <v>0.004625909961760044</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.004136904142796993</v>
+        <v>0.004136894829571247</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.004065119661390781</v>
+        <v>0.004065101034939289</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.2599999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.004421568475663662</v>
+        <v>0.00442154984921217</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.2599999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0058962507173419</v>
+        <v>0.005896224640309811</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.2599999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.002410854212939739</v>
+        <v>0.002410844899713993</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.2599999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.003851224668323994</v>
+        <v>0.003851206041872501</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.2599999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.004623142071068287</v>
+        <v>0.004623127169907093</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.3999999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.002010752446949482</v>
+        <v>0.002010771073400974</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.1199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.002061718143522739</v>
+        <v>0.002061747945845127</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.007035522721707821</v>
+        <v>0.007035505957901478</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.1199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.004081328399479389</v>
+        <v>0.004081348888576031</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.1199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.001831871457397938</v>
+        <v>0.00183189008384943</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.1199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0002589216455817223</v>
+        <v>-0.0002589458599686623</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.3999999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.001307317055761814</v>
+        <v>0.00130730401724577</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.0002074176445603371</v>
+        <v>0.0002074437215924263</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.0008776066824793816</v>
+        <v>0.0008776197209954262</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.0008086906746029854</v>
+        <v>0.0008086925372481346</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.001607649959623814</v>
+        <v>0.001607640646398067</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.002213354222476482</v>
+        <v>0.002213348634541035</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.002100919373333454</v>
+        <v>0.002100936137139797</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.002211947925388813</v>
+        <v>0.002211912535130978</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.001019853167235851</v>
+        <v>0.001019847579300404</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.001627353020012379</v>
+        <v>0.001627379097044468</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.2599999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.00235563050955534</v>
+        <v>0.002355634234845638</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.1199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.002762009389698505</v>
+        <v>0.002761994488537312</v>
       </c>
       <c r="JB80" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.002996171824634075</v>
+        <v>0.002996175549924374</v>
       </c>
       <c r="JB81" t="n">
         <v>0.02000000000000007</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.002552864141762257</v>
+        <v>0.00255283061414957</v>
       </c>
       <c r="JB82" t="n">
         <v>0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.002065935172140598</v>
+        <v>0.002065937034785748</v>
       </c>
       <c r="JB83" t="n">
         <v>0.3</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.002934104762971401</v>
+        <v>0.002934128977358341</v>
       </c>
       <c r="JB84" t="n">
         <v>0.16</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.003941447474062443</v>
+        <v>0.003941456787288189</v>
       </c>
       <c r="JB85" t="n">
         <v>0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002963925711810589</v>
+        <v>-0.002963907085359097</v>
       </c>
       <c r="JB86" t="n">
         <v>0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.07801438868045807</v>
+        <v>0.07801437377929688</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.1199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.01539632584899664</v>
+        <v>-0.01539629977196455</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.7199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.001553810201585293</v>
+        <v>-0.001553821377456188</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.7199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.007292834110558033</v>
+        <v>-0.007292849011719227</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.001219081692397594</v>
+        <v>-0.001219085417687893</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.0002464940771460533</v>
+        <v>0.0002465145662426949</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.0006235865876078606</v>
+        <v>-0.0006236014887690544</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>4.375819116830826e-05</v>
+        <v>4.377122968435287e-05</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>5.811359733343124e-05</v>
+        <v>5.812104791402817e-05</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.0001672981306910515</v>
+        <v>0.0001672962680459023</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.1199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-6.233993917703629e-05</v>
+        <v>-6.234366446733475e-05</v>
       </c>
       <c r="JB99" t="n">
         <v>0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.006320119835436344</v>
+        <v>0.006320132873952389</v>
       </c>
       <c r="JB100" t="n">
         <v>0.1600000000000001</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.006587130017578602</v>
+        <v>0.0065871337428689</v>
       </c>
       <c r="JB101" t="n">
         <v>0.1600000000000001</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.003054832108318806</v>
+        <v>-0.003054852597415447</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.0005223127081990242</v>
+        <v>-0.0005222903564572334</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.001063398085534573</v>
+        <v>-0.001063420437276363</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.0002495450899004936</v>
+        <v>-0.0002495283260941505</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0.3534709084857451</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0004492616280913353</v>
+        <v>0.0004492746666073799</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0.3534707247432859</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.0006792200729250908</v>
+        <v>0.0006792237982153893</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.3</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0.3534703205098759</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.001431002281606197</v>
+        <v>0.001431011594831944</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5799999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0.3534694752945639</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.001804214902222157</v>
+        <v>0.00180418323725462</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0.3534694385460722</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.001552673988044262</v>
+        <v>0.001552718691527843</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9999999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0.3534695855400395</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.001286194659769535</v>
+        <v>0.001286213286221027</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.8599999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0.3534695120430558</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.004203951917588711</v>
+        <v>0.004203923977911472</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
         <v>0.3534695855400395</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.0005159592255949974</v>
+        <v>0.0005159536376595497</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
         <v>0.3534696222885314</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.002637431956827641</v>
+        <v>0.002637452445924282</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
         <v>0.3534695120430558</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>4.78820875287056e-05</v>
+        <v>4.786159843206406e-05</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0.3534699530249578</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.0008846716955304146</v>
+        <v>0.0008846772834658623</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
         <v>0.3534698427794822</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.0003505991771817207</v>
+        <v>0.0003505786880850792</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
         <v>0.3534698060309903</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.0008834348991513252</v>
+        <v>0.0008834498003125191</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.16</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
         <v>0.3534697325340067</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.0007661161944270134</v>
+        <v>0.0007661124691367149</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.02000000000000007</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0.353469695785515</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.0009679654613137245</v>
+        <v>0.0009679915383458138</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.001674908213317394</v>
+        <v>0.001674915663897991</v>
       </c>
       <c r="JB121" t="n">
         <v>0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.00139192771166563</v>
+        <v>0.001391948200762272</v>
       </c>
       <c r="JB122" t="n">
         <v>0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.001267603598535061</v>
+        <v>0.001267592422664165</v>
       </c>
       <c r="JB123" t="n">
         <v>0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.002019877545535564</v>
+        <v>0.002019873820245266</v>
       </c>
       <c r="JB124" t="n">
         <v>0.8599999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.002995423041284084</v>
+        <v>0.002995426766574383</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9299999999999997</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.002213896252214909</v>
+        <v>0.002213901840150356</v>
       </c>
       <c r="JB126" t="n">
         <v>0.9999999999999998</v>
